--- a/p6_deployment/data/france/data_preparation/df_constructed.xlsx
+++ b/p6_deployment/data/france/data_preparation/df_constructed.xlsx
@@ -500,24 +500,24 @@
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
+          <t>h2h_35</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>h2h_3</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
           <t>h2h_35_segun_loc</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>h2h_35</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>h2h_3_segun_loc</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>h2h_3</t>
-        </is>
-      </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
           <t>result</t>
@@ -535,74 +535,74 @@
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_last_match_fouls</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_fouls_against</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_points</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_points_against</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_last_match_interceptions</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_interceptions_against</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_fouls</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_fouls_against</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_shots_on_goal</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_shots_on_goal_against</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_n_matches_last_days</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_n_matches_last_days_against</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goal_attempts</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goal_attempts_against</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_expected_goals_(xg)</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_expected_goals_(xg)_against</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_n_matches_last_days</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_n_matches_last_days_against</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goal_attempts</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goal_attempts_against</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_points</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_points_against</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_shots_on_goal</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_shots_on_goal_against</t>
-        </is>
-      </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_goals</t>
@@ -625,97 +625,97 @@
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_pot_player_start</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_val_player_sub</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_miss</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_val_player_miss</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_miss</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_start</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_sub</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_val_player_start</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_miss</t>
-        </is>
-      </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_start</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_sub</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_start</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_start</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>dif_sum_pot_player_miss</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_sub</t>
-        </is>
-      </c>
-      <c r="AR1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_start</t>
-        </is>
-      </c>
-      <c r="AS1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_val_player_miss</t>
-        </is>
-      </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_sub</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>dif_n_player_miss</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_sub</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_sub</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_rat_player_miss</t>
+        </is>
+      </c>
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_hei_player_miss</t>
-        </is>
-      </c>
-      <c r="AU1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_sub</t>
-        </is>
-      </c>
-      <c r="AV1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_start</t>
-        </is>
-      </c>
-      <c r="AW1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_start</t>
-        </is>
-      </c>
-      <c r="AX1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_start</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_sub</t>
-        </is>
-      </c>
-      <c r="AZ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_rat_player_miss</t>
-        </is>
-      </c>
-      <c r="BA1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_sub</t>
-        </is>
-      </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_n_player_miss</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_sub</t>
-        </is>
-      </c>
-      <c r="BD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_sub</t>
-        </is>
-      </c>
-      <c r="BE1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_start</t>
-        </is>
-      </c>
-      <c r="BF1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_miss</t>
         </is>
       </c>
       <c r="BG1" s="1" t="inlineStr">
@@ -794,10 +794,10 @@
         <v>-3</v>
       </c>
       <c r="Q2" t="n">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="R2" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -823,47 +823,47 @@
       <c r="AL2" t="inlineStr"/>
       <c r="AM2" t="inlineStr"/>
       <c r="AN2" t="n">
-        <v>-11638059.44055944</v>
-      </c>
-      <c r="AO2" t="inlineStr"/>
+        <v>-7.716477272727289</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>-5470845.861314612</v>
+      </c>
       <c r="AP2" t="inlineStr"/>
-      <c r="AQ2" t="n">
-        <v>-5647124.189912653</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>-7.323776223776207</v>
-      </c>
-      <c r="AS2" t="inlineStr"/>
-      <c r="AT2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="n">
+        <v>2.890340909090895</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>4.259765466015466</v>
+      </c>
       <c r="AU2" t="n">
-        <v>-0.3748473748473748</v>
+        <v>-11839000.9469697</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.8174825174825173</v>
+        <v>-7.778598484848487</v>
       </c>
       <c r="AW2" t="n">
-        <v>3.476223776223804</v>
+        <v>-9.221041921041916</v>
       </c>
       <c r="AX2" t="n">
-        <v>-7.793706293706279</v>
+        <v>1.241098484848482</v>
       </c>
       <c r="AY2" t="n">
-        <v>-2.091352024044326</v>
+        <v>-0.4121212121212126</v>
       </c>
       <c r="AZ2" t="inlineStr"/>
       <c r="BA2" t="n">
-        <v>-9.246583544660467</v>
+        <v>-0.3693121693121693</v>
       </c>
       <c r="BB2" t="inlineStr"/>
       <c r="BC2" t="n">
-        <v>3.716669014745975</v>
+        <v>-6.116012922262925</v>
       </c>
       <c r="BD2" t="n">
-        <v>-6.340424532732229</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>-0.4125874125874129</v>
-      </c>
+        <v>-2.31424501424501</v>
+      </c>
+      <c r="BE2" t="inlineStr"/>
       <c r="BF2" t="inlineStr"/>
       <c r="BG2" t="n">
         <v>0</v>
@@ -872,7 +872,7 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>M5VGwpVA</t>
+          <t>ripawyyS</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
@@ -880,24 +880,24 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">wattellier e 
+          <t xml:space="preserve">delajod w 
   fra </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade de la mosson
-  montpellier </t>
+          <t xml:space="preserve">stade de l abbe deschamps
+  auxerre </t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Eyf00syR</t>
+          <t>MTLr36WA</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>nP6UzIU1</t>
+          <t>YagoQJpq</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -924,22 +924,22 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>d0X3cO3I</t>
+          <t>OpNm82MB</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>AaLVdEGK</t>
+          <t>zuUcoUwO</t>
         </is>
       </c>
       <c r="O3" t="n">
-        <v>-4</v>
+        <v>5</v>
       </c>
       <c r="P3" t="n">
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -968,47 +968,47 @@
       <c r="AL3" t="inlineStr"/>
       <c r="AM3" t="inlineStr"/>
       <c r="AN3" t="n">
-        <v>880351.3153513148</v>
-      </c>
-      <c r="AO3" t="inlineStr"/>
+        <v>-8.557820855614963</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>-5224656.617032778</v>
+      </c>
       <c r="AP3" t="inlineStr"/>
-      <c r="AQ3" t="n">
-        <v>433875.8239081581</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>-1.625352425352403</v>
-      </c>
-      <c r="AS3" t="inlineStr"/>
-      <c r="AT3" t="inlineStr"/>
+      <c r="AQ3" t="inlineStr"/>
+      <c r="AR3" t="inlineStr"/>
+      <c r="AS3" t="n">
+        <v>-2.039438502673789</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>0.8602071410701342</v>
+      </c>
       <c r="AU3" t="n">
-        <v>-0.1128323681758101</v>
+        <v>-10832728.94385027</v>
       </c>
       <c r="AV3" t="n">
-        <v>3.021167721167725</v>
+        <v>-6.746323529411754</v>
       </c>
       <c r="AW3" t="n">
-        <v>-1.952258852258836</v>
+        <v>-8.118783617912882</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.67453657453656</v>
+        <v>2.239639037433154</v>
       </c>
       <c r="AY3" t="n">
-        <v>0.3591133554871284</v>
+        <v>-0.3262032085561497</v>
       </c>
       <c r="AZ3" t="inlineStr"/>
       <c r="BA3" t="n">
-        <v>1.330493524053978</v>
+        <v>-0.2483844414958967</v>
       </c>
       <c r="BB3" t="inlineStr"/>
       <c r="BC3" t="n">
-        <v>-1.027409592599554</v>
+        <v>-6.285055329946971</v>
       </c>
       <c r="BD3" t="n">
-        <v>-0.3231441294466464</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>0.1413697413697412</v>
-      </c>
+        <v>-0.5353574444131688</v>
+      </c>
+      <c r="BE3" t="inlineStr"/>
       <c r="BF3" t="inlineStr"/>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1017,7 +1017,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>zkPwWhT1</t>
+          <t>SOLVXEbk</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -1031,18 +1031,18 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">roazhon park
-  rennes </t>
+          <t xml:space="preserve">stade oceane
+  le havre </t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>d2nnj1IE</t>
+          <t>CIEe04GT</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2akflumR</t>
+          <t>CjhkPw0k</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1069,7 +1069,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>SIFtcwDc</t>
+          <t>25Wk0Fko</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -1078,16 +1078,16 @@
         </is>
       </c>
       <c r="O4" t="n">
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="P4" t="n">
-        <v>-8</v>
+        <v>-1</v>
       </c>
       <c r="Q4" t="n">
-        <v>2</v>
+        <v>-3</v>
       </c>
       <c r="R4" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -1113,47 +1113,47 @@
       <c r="AL4" t="inlineStr"/>
       <c r="AM4" t="inlineStr"/>
       <c r="AN4" t="n">
-        <v>648087.54208754</v>
-      </c>
-      <c r="AO4" t="inlineStr"/>
+        <v>-10.54050802139037</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>-31426388.19040365</v>
+      </c>
       <c r="AP4" t="inlineStr"/>
-      <c r="AQ4" t="n">
-        <v>1689905.014690617</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>1.011447811447823</v>
-      </c>
-      <c r="AS4" t="inlineStr"/>
-      <c r="AT4" t="inlineStr"/>
+      <c r="AQ4" t="inlineStr"/>
+      <c r="AR4" t="inlineStr"/>
+      <c r="AS4" t="n">
+        <v>2.32782234105764</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>-2.047914428301908</v>
+      </c>
       <c r="AU4" t="n">
-        <v>-0.1651189545461993</v>
+        <v>-42492634.80392157</v>
       </c>
       <c r="AV4" t="n">
-        <v>-2.684781144781148</v>
+        <v>-10.10394013666073</v>
       </c>
       <c r="AW4" t="n">
-        <v>-0.5409427609427269</v>
+        <v>-10.20194043046379</v>
       </c>
       <c r="AX4" t="n">
-        <v>-0.855757575757579</v>
+        <v>1.145736779560309</v>
       </c>
       <c r="AY4" t="n">
-        <v>-2.486335729400746</v>
+        <v>-1.365210932857991</v>
       </c>
       <c r="AZ4" t="inlineStr"/>
       <c r="BA4" t="n">
-        <v>-1.207923753233359</v>
+        <v>-1.188181787026907</v>
       </c>
       <c r="BB4" t="inlineStr"/>
       <c r="BC4" t="n">
-        <v>2.216089600114401</v>
+        <v>-10.89609927720937</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.079817607000265</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>-0.4030303030303035</v>
-      </c>
+        <v>0.6520528431473771</v>
+      </c>
+      <c r="BE4" t="inlineStr"/>
       <c r="BF4" t="inlineStr"/>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1162,7 +1162,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>6ehlLyFq</t>
+          <t>0js8u60b</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
@@ -1170,24 +1170,24 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">lissorgue r 
+          <t xml:space="preserve">stinat j 
   fra </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadium municipal
-  toulouse </t>
+          <t xml:space="preserve">stade francis le ble
+  brest </t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>MLmY2yB1</t>
+          <t>Cr4VGaUl</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>veuetnGG</t>
+          <t>SblU3Hee</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1219,14 +1219,14 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>YTLwacK1</t>
+          <t>EgvyJSJo</t>
         </is>
       </c>
       <c r="O5" t="n">
-        <v>-1</v>
+        <v>-5</v>
       </c>
       <c r="P5" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1258,47 +1258,47 @@
       <c r="AL5" t="inlineStr"/>
       <c r="AM5" t="inlineStr"/>
       <c r="AN5" t="n">
-        <v>688286.7132867128</v>
-      </c>
-      <c r="AO5" t="inlineStr"/>
+        <v>-2.147954545454553</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>-4818331.279971784</v>
+      </c>
       <c r="AP5" t="inlineStr"/>
-      <c r="AQ5" t="n">
-        <v>1163859.387894714</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>3.18356643356644</v>
-      </c>
-      <c r="AS5" t="inlineStr"/>
-      <c r="AT5" t="inlineStr"/>
+      <c r="AQ5" t="inlineStr"/>
+      <c r="AR5" t="inlineStr"/>
+      <c r="AS5" t="n">
+        <v>-1.865151515151496</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>-4.290719358649881</v>
+      </c>
       <c r="AU5" t="n">
-        <v>-0.1418408986343769</v>
+        <v>-5179386.363636363</v>
       </c>
       <c r="AV5" t="n">
-        <v>-3.48251748251748</v>
+        <v>-2.188181818181818</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.036713286713308</v>
+        <v>-5.058418851458725</v>
       </c>
       <c r="AX5" t="n">
-        <v>-0.6066433566433602</v>
+        <v>-0.1986363636363642</v>
       </c>
       <c r="AY5" t="n">
-        <v>-2.741455153139938</v>
+        <v>-0.3679545454545452</v>
       </c>
       <c r="AZ5" t="inlineStr"/>
       <c r="BA5" t="n">
-        <v>0.4631780256780189</v>
+        <v>-0.0519513653414585</v>
       </c>
       <c r="BB5" t="inlineStr"/>
       <c r="BC5" t="n">
-        <v>0.2072088036761954</v>
+        <v>-3.792648210600021</v>
       </c>
       <c r="BD5" t="n">
-        <v>3.708345549378151</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>-0.4615384615384615</v>
-      </c>
+        <v>-0.8670699932019588</v>
+      </c>
+      <c r="BE5" t="inlineStr"/>
       <c r="BF5" t="inlineStr"/>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1307,7 +1307,7 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>jqSiuc6F</t>
+          <t>fHYrsJy3</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -1315,24 +1315,24 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">delajod w 
+          <t xml:space="preserve">brisard j 
   fra </t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade auguste delaune
-  reims </t>
+          <t xml:space="preserve">stade louis ii
+  monaco </t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>tItR6sEf</t>
+          <t>2PIvr8o4</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>pfDZL71o</t>
+          <t>YL2QybFe</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1359,22 +1359,22 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>SIFtcwDc</t>
+          <t>CWxpUrtf</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>zuUcoUwO</t>
+          <t>tAufB9Mi</t>
         </is>
       </c>
       <c r="O6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q6" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="R6" t="n">
         <v>1</v>
@@ -1403,47 +1403,47 @@
       <c r="AL6" t="inlineStr"/>
       <c r="AM6" t="inlineStr"/>
       <c r="AN6" t="n">
-        <v>-5628642.676767677</v>
-      </c>
-      <c r="AO6" t="inlineStr"/>
+        <v>7.546617490696434</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>7596270.643946451</v>
+      </c>
       <c r="AP6" t="inlineStr"/>
-      <c r="AQ6" t="n">
-        <v>-1984201.338683247</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>-2.729292929292939</v>
-      </c>
-      <c r="AS6" t="inlineStr"/>
-      <c r="AT6" t="inlineStr"/>
+      <c r="AQ6" t="inlineStr"/>
+      <c r="AR6" t="inlineStr"/>
+      <c r="AS6" t="n">
+        <v>1.239616560340238</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>0.7703458355492785</v>
+      </c>
       <c r="AU6" t="n">
-        <v>-0.1110781762097552</v>
+        <v>12913308.74534822</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.70858585858586</v>
+        <v>6.487523258904844</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.877020202020219</v>
+        <v>4.978215283475677</v>
       </c>
       <c r="AX6" t="n">
-        <v>-2.052777777777763</v>
+        <v>-1.127389021796919</v>
       </c>
       <c r="AY6" t="n">
-        <v>-2.960462855857596</v>
+        <v>0.6061868686868686</v>
       </c>
       <c r="AZ6" t="inlineStr"/>
       <c r="BA6" t="n">
-        <v>-3.220526476447532</v>
+        <v>0.1995893094079739</v>
       </c>
       <c r="BB6" t="inlineStr"/>
       <c r="BC6" t="n">
-        <v>2.36545169012274</v>
+        <v>7.739090076896915</v>
       </c>
       <c r="BD6" t="n">
-        <v>0.2235263639868919</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>-0.2184343434343434</v>
-      </c>
+        <v>-2.817144015930502</v>
+      </c>
+      <c r="BE6" t="inlineStr"/>
       <c r="BF6" t="inlineStr"/>
       <c r="BG6" t="n">
         <v>0</v>
@@ -1452,7 +1452,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>ripawyyS</t>
+          <t>M5VGwpVA</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
@@ -1460,24 +1460,24 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">delajod w 
+          <t xml:space="preserve">wattellier e 
   fra </t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade de l abbe deschamps
-  auxerre </t>
+          <t xml:space="preserve">stade de la mosson
+  montpellier </t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>MTLr36WA</t>
+          <t>Eyf00syR</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>YagoQJpq</t>
+          <t>nP6UzIU1</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1504,25 +1504,25 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>OpNm82MB</t>
+          <t>d0X3cO3I</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>zuUcoUwO</t>
+          <t>AaLVdEGK</t>
         </is>
       </c>
       <c r="O7" t="n">
+        <v>-4</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
         <v>5</v>
       </c>
-      <c r="P7" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>-1</v>
-      </c>
       <c r="R7" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1548,47 +1548,47 @@
       <c r="AL7" t="inlineStr"/>
       <c r="AM7" t="inlineStr"/>
       <c r="AN7" t="n">
-        <v>-11016958.04195804</v>
-      </c>
-      <c r="AO7" t="inlineStr"/>
+        <v>-1.699873737373736</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>297530.6903279708</v>
+      </c>
       <c r="AP7" t="inlineStr"/>
-      <c r="AQ7" t="n">
-        <v>-5414538.750722962</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>-8.580419580419587</v>
-      </c>
-      <c r="AS7" t="inlineStr"/>
-      <c r="AT7" t="inlineStr"/>
+      <c r="AQ7" t="inlineStr"/>
+      <c r="AR7" t="inlineStr"/>
+      <c r="AS7" t="n">
+        <v>-2.221854575163377</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>-1.118346064038775</v>
+      </c>
       <c r="AU7" t="n">
-        <v>-0.2810070046912154</v>
+        <v>737196.9696969688</v>
       </c>
       <c r="AV7" t="n">
-        <v>2.244755244755247</v>
+        <v>1.521954842543067</v>
       </c>
       <c r="AW7" t="n">
-        <v>-1.986013986014001</v>
+        <v>1.015734422949777</v>
       </c>
       <c r="AX7" t="n">
-        <v>-6.867132867132867</v>
+        <v>3.078980986333924</v>
       </c>
       <c r="AY7" t="n">
-        <v>-0.5345261463682505</v>
+        <v>0.1570484254307785</v>
       </c>
       <c r="AZ7" t="inlineStr"/>
       <c r="BA7" t="n">
-        <v>-8.122965484807594</v>
+        <v>-0.1049475371252182</v>
       </c>
       <c r="BB7" t="inlineStr"/>
       <c r="BC7" t="n">
-        <v>0.4247149049780603</v>
+        <v>-0.5268338425113512</v>
       </c>
       <c r="BD7" t="n">
-        <v>-6.41577720525089</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>-0.3216783216783221</v>
-      </c>
+        <v>0.2867391716998995</v>
+      </c>
+      <c r="BE7" t="inlineStr"/>
       <c r="BF7" t="inlineStr"/>
       <c r="BG7" t="n">
         <v>0</v>
@@ -1597,7 +1597,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>fHYrsJy3</t>
+          <t>jqSiuc6F</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -1605,24 +1605,24 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">brisard j 
+          <t xml:space="preserve">delajod w 
   fra </t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade louis ii
-  monaco </t>
+          <t xml:space="preserve">stade auguste delaune
+  reims </t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2PIvr8o4</t>
+          <t>tItR6sEf</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>YL2QybFe</t>
+          <t>pfDZL71o</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1649,25 +1649,25 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>CWxpUrtf</t>
+          <t>SIFtcwDc</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>tAufB9Mi</t>
+          <t>zuUcoUwO</t>
         </is>
       </c>
       <c r="O8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -1693,47 +1693,47 @@
       <c r="AL8" t="inlineStr"/>
       <c r="AM8" t="inlineStr"/>
       <c r="AN8" t="n">
-        <v>13040026.70940171</v>
-      </c>
-      <c r="AO8" t="inlineStr"/>
+        <v>-2.674159867909864</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>-1820081.427694503</v>
+      </c>
       <c r="AP8" t="inlineStr"/>
-      <c r="AQ8" t="n">
-        <v>8273859.188358511</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>7.604817404817396</v>
-      </c>
-      <c r="AS8" t="inlineStr"/>
-      <c r="AT8" t="inlineStr"/>
+      <c r="AQ8" t="inlineStr"/>
+      <c r="AR8" t="inlineStr"/>
+      <c r="AS8" t="n">
+        <v>2.050121406371346</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>2.1298524824347</v>
+      </c>
       <c r="AU8" t="n">
-        <v>0.2540227574283302</v>
+        <v>-5610518.162393162</v>
       </c>
       <c r="AV8" t="n">
-        <v>-1.081390831390827</v>
+        <v>-2.064908702408701</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.8835858585858887</v>
+        <v>-3.102359598247745</v>
       </c>
       <c r="AX8" t="n">
-        <v>6.537694250194264</v>
+        <v>1.666938616938619</v>
       </c>
       <c r="AY8" t="n">
-        <v>-2.70238134973042</v>
+        <v>-0.2295114607614608</v>
       </c>
       <c r="AZ8" t="inlineStr"/>
       <c r="BA8" t="n">
-        <v>5.307496659257509</v>
+        <v>-0.129117331255489</v>
       </c>
       <c r="BB8" t="inlineStr"/>
       <c r="BC8" t="n">
-        <v>1.320027839377701</v>
+        <v>0.1884778385600754</v>
       </c>
       <c r="BD8" t="n">
-        <v>7.734674924748461</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>0.5866355866355866</v>
-      </c>
+        <v>-2.957233642332326</v>
+      </c>
+      <c r="BE8" t="inlineStr"/>
       <c r="BF8" t="inlineStr"/>
       <c r="BG8" t="n">
         <v>0</v>
@@ -1742,7 +1742,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>SOLVXEbk</t>
+          <t>6ehlLyFq</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
@@ -1750,24 +1750,24 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">letexier f 
+          <t xml:space="preserve">lissorgue r 
   fra </t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade oceane
-  le havre </t>
+          <t xml:space="preserve">stadium municipal
+  toulouse </t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>CIEe04GT</t>
+          <t>MLmY2yB1</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CjhkPw0k</t>
+          <t>veuetnGG</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1794,22 +1794,22 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>25Wk0Fko</t>
+          <t>UapruDaf</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>8MdrBIUb</t>
+          <t>YTLwacK1</t>
         </is>
       </c>
       <c r="O9" t="n">
-        <v>-9</v>
+        <v>-1</v>
       </c>
       <c r="P9" t="n">
-        <v>-9</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="R9" t="n">
         <v>-1</v>
@@ -1838,47 +1838,47 @@
       <c r="AL9" t="inlineStr"/>
       <c r="AM9" t="inlineStr"/>
       <c r="AN9" t="n">
-        <v>-42645576.92307692</v>
-      </c>
-      <c r="AO9" t="inlineStr"/>
+        <v>3.048484848484875</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>1274509.437020306</v>
+      </c>
       <c r="AP9" t="inlineStr"/>
-      <c r="AQ9" t="n">
-        <v>-31243317.71680195</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>-10.50646853146851</v>
-      </c>
-      <c r="AS9" t="inlineStr"/>
-      <c r="AT9" t="inlineStr"/>
+      <c r="AQ9" t="inlineStr"/>
+      <c r="AR9" t="inlineStr"/>
+      <c r="AS9" t="n">
+        <v>0.6909090909091447</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>0.209326703891918</v>
+      </c>
       <c r="AU9" t="n">
-        <v>-1.199077882615035</v>
+        <v>734848.4848484844</v>
       </c>
       <c r="AV9" t="n">
-        <v>1.347824397824393</v>
+        <v>-0.5333333333333314</v>
       </c>
       <c r="AW9" t="n">
-        <v>2.772358197358216</v>
+        <v>0.995827320827317</v>
       </c>
       <c r="AX9" t="n">
-        <v>-9.863655788655791</v>
+        <v>-3.406060606060603</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.5081321002848149</v>
+        <v>-0.4545454545454541</v>
       </c>
       <c r="AZ9" t="inlineStr"/>
       <c r="BA9" t="n">
-        <v>-10.08058719190701</v>
+        <v>-0.1304039358387183</v>
       </c>
       <c r="BB9" t="inlineStr"/>
       <c r="BC9" t="n">
-        <v>-2.275850698784467</v>
+        <v>4.086959658698802</v>
       </c>
       <c r="BD9" t="n">
-        <v>-10.62581463426967</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>-1.368181818181818</v>
-      </c>
+        <v>-2.63731570362005</v>
+      </c>
+      <c r="BE9" t="inlineStr"/>
       <c r="BF9" t="inlineStr"/>
       <c r="BG9" t="n">
         <v>0</v>
@@ -1887,7 +1887,7 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>0js8u60b</t>
+          <t>zkPwWhT1</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -1895,24 +1895,24 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">stinat j 
+          <t xml:space="preserve">letexier f 
   fra </t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade francis le ble
-  brest </t>
+          <t xml:space="preserve">roazhon park
+  rennes </t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Cr4VGaUl</t>
+          <t>d2nnj1IE</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>SblU3Hee</t>
+          <t>2akflumR</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1939,22 +1939,22 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>UapruDaf</t>
+          <t>SIFtcwDc</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>EgvyJSJo</t>
+          <t>8MdrBIUb</t>
         </is>
       </c>
       <c r="O10" t="n">
+        <v>-8</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q10" t="n">
         <v>-5</v>
-      </c>
-      <c r="P10" t="n">
-        <v>-5</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>1</v>
       </c>
       <c r="R10" t="n">
         <v>1</v>
@@ -1983,47 +1983,47 @@
       <c r="AL10" t="inlineStr"/>
       <c r="AM10" t="inlineStr"/>
       <c r="AN10" t="n">
-        <v>-5294965.034965037</v>
-      </c>
-      <c r="AO10" t="inlineStr"/>
+        <v>0.9887293992557176</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>1569062.032390579</v>
+      </c>
       <c r="AP10" t="inlineStr"/>
-      <c r="AQ10" t="n">
-        <v>-5066769.561063292</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>-2.006293706293718</v>
-      </c>
-      <c r="AS10" t="inlineStr"/>
-      <c r="AT10" t="inlineStr"/>
+      <c r="AQ10" t="inlineStr"/>
+      <c r="AR10" t="inlineStr"/>
+      <c r="AS10" t="n">
+        <v>-0.4876129718234949</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>1.835751837832817</v>
+      </c>
       <c r="AU10" t="n">
-        <v>-0.08418075732317254</v>
+        <v>736741.0951621458</v>
       </c>
       <c r="AV10" t="n">
-        <v>-0.3265734265734288</v>
+        <v>-0.8248272195640425</v>
       </c>
       <c r="AW10" t="n">
-        <v>-1.786013986014012</v>
+        <v>-1.185964125243629</v>
       </c>
       <c r="AX10" t="n">
-        <v>-2.206293706293707</v>
+        <v>-2.613024986709199</v>
       </c>
       <c r="AY10" t="n">
-        <v>-0.8186544793355885</v>
+        <v>-0.4108984582668798</v>
       </c>
       <c r="AZ10" t="inlineStr"/>
       <c r="BA10" t="n">
-        <v>-4.964617142403512</v>
+        <v>-0.1143865876186227</v>
       </c>
       <c r="BB10" t="inlineStr"/>
       <c r="BC10" t="n">
-        <v>-4.252072016390883</v>
+        <v>0.9072912603301972</v>
       </c>
       <c r="BD10" t="n">
-        <v>-3.933407047029334</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>-0.3692307692307688</v>
-      </c>
+        <v>-2.236535586981653</v>
+      </c>
+      <c r="BE10" t="inlineStr"/>
       <c r="BF10" t="inlineStr"/>
       <c r="BG10" t="n">
         <v>0</v>

--- a/p6_deployment/data/france/data_preparation/df_constructed.xlsx
+++ b/p6_deployment/data/france/data_preparation/df_constructed.xlsx
@@ -525,94 +525,94 @@
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_last_match_n_matches_last_days</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_n_matches_last_days_against</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goal_attempts</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goal_attempts_against</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_expected_goals_(xg)</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_expected_goals_(xg)_against</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_last_match_ball_possession</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_ball_possession_against</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_fouls</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_fouls_against</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_points</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_points_against</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_shots_on_goal</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_shots_on_goal_against</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goals</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goals_against</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_interceptions</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_interceptions_against</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_shots_on_goal</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_shots_on_goal_against</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_n_matches_last_days</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_n_matches_last_days_against</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goal_attempts</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goal_attempts_against</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_expected_goals_(xg)</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_expected_goals_(xg)_against</t>
-        </is>
-      </c>
-      <c r="AJ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goals</t>
-        </is>
-      </c>
-      <c r="AK1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goals_against</t>
-        </is>
-      </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>mean_last_match_mean_rat_player_start_home_against</t>
@@ -625,97 +625,97 @@
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_hei_player_miss</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_start</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_val_player_start</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_pot_player_start</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_rat_player_miss</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_miss</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_sub</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_miss</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_start</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_start</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_pot_player_miss</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_sub</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_start</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_sub</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_val_player_miss</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>dif_n_player_miss</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_sub</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_sub</t>
+        </is>
+      </c>
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_val_player_sub</t>
-        </is>
-      </c>
-      <c r="AP1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_miss</t>
-        </is>
-      </c>
-      <c r="AQ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_val_player_miss</t>
-        </is>
-      </c>
-      <c r="AR1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_miss</t>
-        </is>
-      </c>
-      <c r="AS1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_start</t>
-        </is>
-      </c>
-      <c r="AT1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_sub</t>
-        </is>
-      </c>
-      <c r="AU1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_start</t>
-        </is>
-      </c>
-      <c r="AV1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_start</t>
-        </is>
-      </c>
-      <c r="AW1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_sub</t>
-        </is>
-      </c>
-      <c r="AX1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_start</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_start</t>
-        </is>
-      </c>
-      <c r="AZ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_pot_player_miss</t>
-        </is>
-      </c>
-      <c r="BA1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_sub</t>
-        </is>
-      </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_n_player_miss</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_sub</t>
-        </is>
-      </c>
-      <c r="BD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_sub</t>
-        </is>
-      </c>
-      <c r="BE1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_rat_player_miss</t>
-        </is>
-      </c>
-      <c r="BF1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_miss</t>
         </is>
       </c>
       <c r="BG1" s="1" t="inlineStr">
@@ -822,49 +822,49 @@
       <c r="AK2" t="inlineStr"/>
       <c r="AL2" t="inlineStr"/>
       <c r="AM2" t="inlineStr"/>
-      <c r="AN2" t="n">
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="n">
+        <v>-7.778598484848487</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>-11839000.9469697</v>
+      </c>
+      <c r="AQ2" t="n">
         <v>-7.716477272727289</v>
       </c>
-      <c r="AO2" t="n">
-        <v>-5470845.861314612</v>
-      </c>
-      <c r="AP2" t="inlineStr"/>
-      <c r="AQ2" t="inlineStr"/>
       <c r="AR2" t="inlineStr"/>
-      <c r="AS2" t="n">
-        <v>2.890340909090895</v>
-      </c>
+      <c r="AS2" t="inlineStr"/>
       <c r="AT2" t="n">
         <v>4.259765466015466</v>
       </c>
-      <c r="AU2" t="n">
-        <v>-11839000.9469697</v>
-      </c>
+      <c r="AU2" t="inlineStr"/>
       <c r="AV2" t="n">
-        <v>-7.778598484848487</v>
+        <v>-0.4121212121212126</v>
       </c>
       <c r="AW2" t="n">
-        <v>-9.221041921041916</v>
-      </c>
-      <c r="AX2" t="n">
         <v>1.241098484848482</v>
       </c>
+      <c r="AX2" t="inlineStr"/>
       <c r="AY2" t="n">
-        <v>-0.4121212121212126</v>
-      </c>
-      <c r="AZ2" t="inlineStr"/>
+        <v>-2.31424501424501</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>2.890340909090895</v>
+      </c>
       <c r="BA2" t="n">
         <v>-0.3693121693121693</v>
       </c>
       <c r="BB2" t="inlineStr"/>
-      <c r="BC2" t="n">
+      <c r="BC2" t="inlineStr"/>
+      <c r="BD2" t="n">
+        <v>-9.221041921041916</v>
+      </c>
+      <c r="BE2" t="n">
         <v>-6.116012922262925</v>
       </c>
-      <c r="BD2" t="n">
-        <v>-2.31424501424501</v>
-      </c>
-      <c r="BE2" t="inlineStr"/>
-      <c r="BF2" t="inlineStr"/>
+      <c r="BF2" t="n">
+        <v>-5470845.861314612</v>
+      </c>
       <c r="BG2" t="n">
         <v>0</v>
       </c>
@@ -967,49 +967,49 @@
       <c r="AK3" t="inlineStr"/>
       <c r="AL3" t="inlineStr"/>
       <c r="AM3" t="inlineStr"/>
-      <c r="AN3" t="n">
+      <c r="AN3" t="inlineStr"/>
+      <c r="AO3" t="n">
+        <v>-6.746323529411754</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>-10832728.94385027</v>
+      </c>
+      <c r="AQ3" t="n">
         <v>-8.557820855614963</v>
       </c>
-      <c r="AO3" t="n">
-        <v>-5224656.617032778</v>
-      </c>
-      <c r="AP3" t="inlineStr"/>
-      <c r="AQ3" t="inlineStr"/>
       <c r="AR3" t="inlineStr"/>
-      <c r="AS3" t="n">
-        <v>-2.039438502673789</v>
-      </c>
+      <c r="AS3" t="inlineStr"/>
       <c r="AT3" t="n">
         <v>0.8602071410701342</v>
       </c>
-      <c r="AU3" t="n">
-        <v>-10832728.94385027</v>
-      </c>
+      <c r="AU3" t="inlineStr"/>
       <c r="AV3" t="n">
-        <v>-6.746323529411754</v>
+        <v>-0.3262032085561497</v>
       </c>
       <c r="AW3" t="n">
-        <v>-8.118783617912882</v>
-      </c>
-      <c r="AX3" t="n">
         <v>2.239639037433154</v>
       </c>
+      <c r="AX3" t="inlineStr"/>
       <c r="AY3" t="n">
-        <v>-0.3262032085561497</v>
-      </c>
-      <c r="AZ3" t="inlineStr"/>
+        <v>-0.5353574444131688</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>-2.039438502673789</v>
+      </c>
       <c r="BA3" t="n">
         <v>-0.2483844414958967</v>
       </c>
       <c r="BB3" t="inlineStr"/>
-      <c r="BC3" t="n">
+      <c r="BC3" t="inlineStr"/>
+      <c r="BD3" t="n">
+        <v>-8.118783617912882</v>
+      </c>
+      <c r="BE3" t="n">
         <v>-6.285055329946971</v>
       </c>
-      <c r="BD3" t="n">
-        <v>-0.5353574444131688</v>
-      </c>
-      <c r="BE3" t="inlineStr"/>
-      <c r="BF3" t="inlineStr"/>
+      <c r="BF3" t="n">
+        <v>-5224656.617032778</v>
+      </c>
       <c r="BG3" t="n">
         <v>0</v>
       </c>
@@ -1112,49 +1112,49 @@
       <c r="AK4" t="inlineStr"/>
       <c r="AL4" t="inlineStr"/>
       <c r="AM4" t="inlineStr"/>
-      <c r="AN4" t="n">
-        <v>-10.54050802139037</v>
-      </c>
+      <c r="AN4" t="inlineStr"/>
       <c r="AO4" t="n">
-        <v>-31426388.19040365</v>
-      </c>
-      <c r="AP4" t="inlineStr"/>
-      <c r="AQ4" t="inlineStr"/>
+        <v>-10.07929292929293</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>-42145729.16666666</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>-10.52386363636361</v>
+      </c>
       <c r="AR4" t="inlineStr"/>
-      <c r="AS4" t="n">
-        <v>2.32782234105764</v>
-      </c>
+      <c r="AS4" t="inlineStr"/>
       <c r="AT4" t="n">
-        <v>-2.047914428301908</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>-42492634.80392157</v>
-      </c>
+        <v>-2.114194868609758</v>
+      </c>
+      <c r="AU4" t="inlineStr"/>
       <c r="AV4" t="n">
-        <v>-10.10394013666073</v>
+        <v>-1.363036616161616</v>
       </c>
       <c r="AW4" t="n">
-        <v>-10.20194043046379</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>1.145736779560309</v>
-      </c>
+        <v>1.113226010101009</v>
+      </c>
+      <c r="AX4" t="inlineStr"/>
       <c r="AY4" t="n">
-        <v>-1.365210932857991</v>
-      </c>
-      <c r="AZ4" t="inlineStr"/>
+        <v>0.6490451249785458</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>2.375157828282823</v>
+      </c>
       <c r="BA4" t="n">
-        <v>-1.188181787026907</v>
+        <v>-1.206572838687132</v>
       </c>
       <c r="BB4" t="inlineStr"/>
-      <c r="BC4" t="n">
-        <v>-10.89609927720937</v>
-      </c>
+      <c r="BC4" t="inlineStr"/>
       <c r="BD4" t="n">
-        <v>0.6520528431473771</v>
-      </c>
-      <c r="BE4" t="inlineStr"/>
-      <c r="BF4" t="inlineStr"/>
+        <v>-10.42513491550108</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>-10.95948354519788</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>-32537750.59894048</v>
+      </c>
       <c r="BG4" t="n">
         <v>0</v>
       </c>
@@ -1257,49 +1257,49 @@
       <c r="AK5" t="inlineStr"/>
       <c r="AL5" t="inlineStr"/>
       <c r="AM5" t="inlineStr"/>
-      <c r="AN5" t="n">
+      <c r="AN5" t="inlineStr"/>
+      <c r="AO5" t="n">
+        <v>-2.188181818181818</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>-5179386.363636363</v>
+      </c>
+      <c r="AQ5" t="n">
         <v>-2.147954545454553</v>
       </c>
-      <c r="AO5" t="n">
-        <v>-4818331.279971784</v>
-      </c>
-      <c r="AP5" t="inlineStr"/>
-      <c r="AQ5" t="inlineStr"/>
       <c r="AR5" t="inlineStr"/>
-      <c r="AS5" t="n">
-        <v>-1.865151515151496</v>
-      </c>
+      <c r="AS5" t="inlineStr"/>
       <c r="AT5" t="n">
         <v>-4.290719358649881</v>
       </c>
-      <c r="AU5" t="n">
-        <v>-5179386.363636363</v>
-      </c>
+      <c r="AU5" t="inlineStr"/>
       <c r="AV5" t="n">
-        <v>-2.188181818181818</v>
+        <v>-0.3679545454545452</v>
       </c>
       <c r="AW5" t="n">
-        <v>-5.058418851458725</v>
-      </c>
-      <c r="AX5" t="n">
         <v>-0.1986363636363642</v>
       </c>
+      <c r="AX5" t="inlineStr"/>
       <c r="AY5" t="n">
-        <v>-0.3679545454545452</v>
-      </c>
-      <c r="AZ5" t="inlineStr"/>
+        <v>-0.8670699932019588</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>-1.865151515151496</v>
+      </c>
       <c r="BA5" t="n">
         <v>-0.0519513653414585</v>
       </c>
       <c r="BB5" t="inlineStr"/>
-      <c r="BC5" t="n">
+      <c r="BC5" t="inlineStr"/>
+      <c r="BD5" t="n">
+        <v>-5.058418851458725</v>
+      </c>
+      <c r="BE5" t="n">
         <v>-3.792648210600021</v>
       </c>
-      <c r="BD5" t="n">
-        <v>-0.8670699932019588</v>
-      </c>
-      <c r="BE5" t="inlineStr"/>
-      <c r="BF5" t="inlineStr"/>
+      <c r="BF5" t="n">
+        <v>-4818331.279971784</v>
+      </c>
       <c r="BG5" t="n">
         <v>0</v>
       </c>
@@ -1402,49 +1402,49 @@
       <c r="AK6" t="inlineStr"/>
       <c r="AL6" t="inlineStr"/>
       <c r="AM6" t="inlineStr"/>
-      <c r="AN6" t="n">
+      <c r="AN6" t="inlineStr"/>
+      <c r="AO6" t="n">
+        <v>6.487523258904844</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>12913308.74534822</v>
+      </c>
+      <c r="AQ6" t="n">
         <v>7.546617490696434</v>
       </c>
-      <c r="AO6" t="n">
-        <v>7596270.643946451</v>
-      </c>
-      <c r="AP6" t="inlineStr"/>
-      <c r="AQ6" t="inlineStr"/>
       <c r="AR6" t="inlineStr"/>
-      <c r="AS6" t="n">
-        <v>1.239616560340238</v>
-      </c>
+      <c r="AS6" t="inlineStr"/>
       <c r="AT6" t="n">
         <v>0.7703458355492785</v>
       </c>
-      <c r="AU6" t="n">
-        <v>12913308.74534822</v>
-      </c>
+      <c r="AU6" t="inlineStr"/>
       <c r="AV6" t="n">
-        <v>6.487523258904844</v>
+        <v>0.6061868686868686</v>
       </c>
       <c r="AW6" t="n">
-        <v>4.978215283475677</v>
-      </c>
-      <c r="AX6" t="n">
         <v>-1.127389021796919</v>
       </c>
+      <c r="AX6" t="inlineStr"/>
       <c r="AY6" t="n">
-        <v>0.6061868686868686</v>
-      </c>
-      <c r="AZ6" t="inlineStr"/>
+        <v>-2.817144015930502</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>1.239616560340238</v>
+      </c>
       <c r="BA6" t="n">
         <v>0.1995893094079739</v>
       </c>
       <c r="BB6" t="inlineStr"/>
-      <c r="BC6" t="n">
+      <c r="BC6" t="inlineStr"/>
+      <c r="BD6" t="n">
+        <v>4.978215283475677</v>
+      </c>
+      <c r="BE6" t="n">
         <v>7.739090076896915</v>
       </c>
-      <c r="BD6" t="n">
-        <v>-2.817144015930502</v>
-      </c>
-      <c r="BE6" t="inlineStr"/>
-      <c r="BF6" t="inlineStr"/>
+      <c r="BF6" t="n">
+        <v>7596270.643946451</v>
+      </c>
       <c r="BG6" t="n">
         <v>0</v>
       </c>
@@ -1547,49 +1547,49 @@
       <c r="AK7" t="inlineStr"/>
       <c r="AL7" t="inlineStr"/>
       <c r="AM7" t="inlineStr"/>
-      <c r="AN7" t="n">
-        <v>-1.699873737373736</v>
-      </c>
+      <c r="AN7" t="inlineStr"/>
       <c r="AO7" t="n">
-        <v>297530.6903279708</v>
-      </c>
-      <c r="AP7" t="inlineStr"/>
-      <c r="AQ7" t="inlineStr"/>
+        <v>1.563383838383828</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>774507.5757575752</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>-1.714141414141409</v>
+      </c>
       <c r="AR7" t="inlineStr"/>
-      <c r="AS7" t="n">
-        <v>-2.221854575163377</v>
-      </c>
+      <c r="AS7" t="inlineStr"/>
       <c r="AT7" t="n">
         <v>-1.118346064038775</v>
       </c>
-      <c r="AU7" t="n">
-        <v>737196.9696969688</v>
-      </c>
+      <c r="AU7" t="inlineStr"/>
       <c r="AV7" t="n">
-        <v>1.521954842543067</v>
+        <v>0.1571338383838383</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.015734422949777</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>3.078980986333924</v>
-      </c>
+        <v>3.099116161616163</v>
+      </c>
+      <c r="AX7" t="inlineStr"/>
       <c r="AY7" t="n">
-        <v>0.1570484254307785</v>
-      </c>
-      <c r="AZ7" t="inlineStr"/>
+        <v>0.2867391716998995</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>-2.1883838383838</v>
+      </c>
       <c r="BA7" t="n">
         <v>-0.1049475371252182</v>
       </c>
       <c r="BB7" t="inlineStr"/>
-      <c r="BC7" t="n">
+      <c r="BC7" t="inlineStr"/>
+      <c r="BD7" t="n">
+        <v>1.015734422949777</v>
+      </c>
+      <c r="BE7" t="n">
         <v>-0.5268338425113512</v>
       </c>
-      <c r="BD7" t="n">
-        <v>0.2867391716998995</v>
-      </c>
-      <c r="BE7" t="inlineStr"/>
-      <c r="BF7" t="inlineStr"/>
+      <c r="BF7" t="n">
+        <v>297530.6903279708</v>
+      </c>
       <c r="BG7" t="n">
         <v>0</v>
       </c>
@@ -1692,49 +1692,49 @@
       <c r="AK8" t="inlineStr"/>
       <c r="AL8" t="inlineStr"/>
       <c r="AM8" t="inlineStr"/>
-      <c r="AN8" t="n">
+      <c r="AN8" t="inlineStr"/>
+      <c r="AO8" t="n">
+        <v>-2.064908702408701</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>-5610518.162393162</v>
+      </c>
+      <c r="AQ8" t="n">
         <v>-2.674159867909864</v>
       </c>
-      <c r="AO8" t="n">
-        <v>-1820081.427694503</v>
-      </c>
-      <c r="AP8" t="inlineStr"/>
-      <c r="AQ8" t="inlineStr"/>
       <c r="AR8" t="inlineStr"/>
-      <c r="AS8" t="n">
-        <v>2.050121406371346</v>
-      </c>
+      <c r="AS8" t="inlineStr"/>
       <c r="AT8" t="n">
         <v>2.1298524824347</v>
       </c>
-      <c r="AU8" t="n">
-        <v>-5610518.162393162</v>
-      </c>
+      <c r="AU8" t="inlineStr"/>
       <c r="AV8" t="n">
-        <v>-2.064908702408701</v>
+        <v>-0.2295114607614608</v>
       </c>
       <c r="AW8" t="n">
-        <v>-3.102359598247745</v>
-      </c>
-      <c r="AX8" t="n">
         <v>1.666938616938619</v>
       </c>
+      <c r="AX8" t="inlineStr"/>
       <c r="AY8" t="n">
-        <v>-0.2295114607614608</v>
-      </c>
-      <c r="AZ8" t="inlineStr"/>
+        <v>-2.957233642332326</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>2.050121406371346</v>
+      </c>
       <c r="BA8" t="n">
         <v>-0.129117331255489</v>
       </c>
       <c r="BB8" t="inlineStr"/>
-      <c r="BC8" t="n">
+      <c r="BC8" t="inlineStr"/>
+      <c r="BD8" t="n">
+        <v>-3.102359598247745</v>
+      </c>
+      <c r="BE8" t="n">
         <v>0.1884778385600754</v>
       </c>
-      <c r="BD8" t="n">
-        <v>-2.957233642332326</v>
-      </c>
-      <c r="BE8" t="inlineStr"/>
-      <c r="BF8" t="inlineStr"/>
+      <c r="BF8" t="n">
+        <v>-1820081.427694503</v>
+      </c>
       <c r="BG8" t="n">
         <v>0</v>
       </c>
@@ -1837,49 +1837,49 @@
       <c r="AK9" t="inlineStr"/>
       <c r="AL9" t="inlineStr"/>
       <c r="AM9" t="inlineStr"/>
-      <c r="AN9" t="n">
+      <c r="AN9" t="inlineStr"/>
+      <c r="AO9" t="n">
+        <v>-0.5333333333333314</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>734848.4848484844</v>
+      </c>
+      <c r="AQ9" t="n">
         <v>3.048484848484875</v>
       </c>
-      <c r="AO9" t="n">
-        <v>1274509.437020306</v>
-      </c>
-      <c r="AP9" t="inlineStr"/>
-      <c r="AQ9" t="inlineStr"/>
       <c r="AR9" t="inlineStr"/>
-      <c r="AS9" t="n">
-        <v>0.6909090909091447</v>
-      </c>
+      <c r="AS9" t="inlineStr"/>
       <c r="AT9" t="n">
         <v>0.209326703891918</v>
       </c>
-      <c r="AU9" t="n">
-        <v>734848.4848484844</v>
-      </c>
+      <c r="AU9" t="inlineStr"/>
       <c r="AV9" t="n">
-        <v>-0.5333333333333314</v>
+        <v>-0.4545454545454541</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.995827320827317</v>
-      </c>
-      <c r="AX9" t="n">
         <v>-3.406060606060603</v>
       </c>
+      <c r="AX9" t="inlineStr"/>
       <c r="AY9" t="n">
-        <v>-0.4545454545454541</v>
-      </c>
-      <c r="AZ9" t="inlineStr"/>
+        <v>-2.63731570362005</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>0.6909090909091447</v>
+      </c>
       <c r="BA9" t="n">
         <v>-0.1304039358387183</v>
       </c>
       <c r="BB9" t="inlineStr"/>
-      <c r="BC9" t="n">
+      <c r="BC9" t="inlineStr"/>
+      <c r="BD9" t="n">
+        <v>0.995827320827317</v>
+      </c>
+      <c r="BE9" t="n">
         <v>4.086959658698802</v>
       </c>
-      <c r="BD9" t="n">
-        <v>-2.63731570362005</v>
-      </c>
-      <c r="BE9" t="inlineStr"/>
-      <c r="BF9" t="inlineStr"/>
+      <c r="BF9" t="n">
+        <v>1274509.437020306</v>
+      </c>
       <c r="BG9" t="n">
         <v>0</v>
       </c>
@@ -1982,49 +1982,49 @@
       <c r="AK10" t="inlineStr"/>
       <c r="AL10" t="inlineStr"/>
       <c r="AM10" t="inlineStr"/>
-      <c r="AN10" t="n">
+      <c r="AN10" t="inlineStr"/>
+      <c r="AO10" t="n">
+        <v>-0.8248272195640425</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>736741.0951621458</v>
+      </c>
+      <c r="AQ10" t="n">
         <v>0.9887293992557176</v>
       </c>
-      <c r="AO10" t="n">
-        <v>1569062.032390579</v>
-      </c>
-      <c r="AP10" t="inlineStr"/>
-      <c r="AQ10" t="inlineStr"/>
       <c r="AR10" t="inlineStr"/>
-      <c r="AS10" t="n">
-        <v>-0.4876129718234949</v>
-      </c>
+      <c r="AS10" t="inlineStr"/>
       <c r="AT10" t="n">
         <v>1.835751837832817</v>
       </c>
-      <c r="AU10" t="n">
-        <v>736741.0951621458</v>
-      </c>
+      <c r="AU10" t="inlineStr"/>
       <c r="AV10" t="n">
-        <v>-0.8248272195640425</v>
+        <v>-0.4108984582668798</v>
       </c>
       <c r="AW10" t="n">
-        <v>-1.185964125243629</v>
-      </c>
-      <c r="AX10" t="n">
         <v>-2.613024986709199</v>
       </c>
+      <c r="AX10" t="inlineStr"/>
       <c r="AY10" t="n">
-        <v>-0.4108984582668798</v>
-      </c>
-      <c r="AZ10" t="inlineStr"/>
+        <v>-2.236535586981653</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>-0.4876129718234949</v>
+      </c>
       <c r="BA10" t="n">
         <v>-0.1143865876186227</v>
       </c>
       <c r="BB10" t="inlineStr"/>
-      <c r="BC10" t="n">
+      <c r="BC10" t="inlineStr"/>
+      <c r="BD10" t="n">
+        <v>-1.185964125243629</v>
+      </c>
+      <c r="BE10" t="n">
         <v>0.9072912603301972</v>
       </c>
-      <c r="BD10" t="n">
-        <v>-2.236535586981653</v>
-      </c>
-      <c r="BE10" t="inlineStr"/>
-      <c r="BF10" t="inlineStr"/>
+      <c r="BF10" t="n">
+        <v>1569062.032390579</v>
+      </c>
       <c r="BG10" t="n">
         <v>0</v>
       </c>

--- a/p6_deployment/data/france/data_preparation/df_constructed.xlsx
+++ b/p6_deployment/data/france/data_preparation/df_constructed.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BG10"/>
+  <dimension ref="A1:BE10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -450,277 +450,267 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>capacity</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>id_team_home</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>id_team_away</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>id_country</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>id_competition</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>is_cup</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>season</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>country</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>competition</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>id_coach_home</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>id_coach_away</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>h2h_35</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>h2h_3</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>h2h_35_segun_loc</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>h2h_3_segun_loc</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>result</t>
-        </is>
-      </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_hei_player_start</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_start</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_start</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_val_player_start</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_sub</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_start</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_sub</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_start</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_sub</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_val_player_sub</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_sub</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_sub</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>is_rival_match</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_ball_possession</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_ball_possession_against</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_last_match_n_matches_last_days</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_n_matches_last_days_against</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_points</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_points_against</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_goal_attempts</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_goal_attempts_against</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_shots_on_goal</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_shots_on_goal_against</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goals</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goals_against</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_expected_goals_(xg)</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_expected_goals_(xg)_against</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_ball_possession</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_ball_possession_against</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_fouls</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_fouls_against</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_points</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_points_against</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_shots_on_goal</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_shots_on_goal_against</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goals</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goals_against</t>
-        </is>
-      </c>
-      <c r="AJ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_interceptions</t>
-        </is>
-      </c>
-      <c r="AK1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_interceptions_against</t>
-        </is>
-      </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>mean_last_match_mean_rat_player_start_home_against</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>mean_last_match_mean_rat_player_start_away_against</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_rat_player_miss</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_val_player_miss</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_miss</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>dif_n_player_miss</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_miss</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_hei_player_miss</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_start</t>
-        </is>
-      </c>
-      <c r="AP1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_start</t>
-        </is>
-      </c>
-      <c r="AQ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_start</t>
-        </is>
-      </c>
-      <c r="AR1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_rat_player_miss</t>
-        </is>
-      </c>
-      <c r="AS1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_miss</t>
-        </is>
-      </c>
-      <c r="AT1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_sub</t>
-        </is>
-      </c>
-      <c r="AU1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_miss</t>
-        </is>
-      </c>
-      <c r="AV1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_start</t>
-        </is>
-      </c>
-      <c r="AW1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_start</t>
-        </is>
-      </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>dif_sum_pot_player_miss</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_sub</t>
-        </is>
-      </c>
-      <c r="AZ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_start</t>
-        </is>
-      </c>
-      <c r="BA1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_sub</t>
-        </is>
-      </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_val_player_miss</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_n_player_miss</t>
-        </is>
-      </c>
-      <c r="BD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_sub</t>
-        </is>
-      </c>
-      <c r="BE1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_sub</t>
-        </is>
-      </c>
-      <c r="BF1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_sub</t>
-        </is>
-      </c>
-      <c r="BG1" s="1" t="inlineStr">
-        <is>
-          <t>is_rival_match</t>
         </is>
       </c>
     </row>
@@ -745,76 +735,102 @@
   angers </t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" t="n">
+        <v>18752</v>
+      </c>
+      <c r="F2" t="inlineStr">
         <is>
           <t>SAlF91iL</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>IBmris38</t>
         </is>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="n">
         <v>55</v>
       </c>
-      <c r="H2" t="n">
+      <c r="I2" t="n">
         <v>551</v>
       </c>
-      <c r="I2" t="n">
-        <v>0</v>
-      </c>
       <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
         <v>20242025</v>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>france</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>ligue 1</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>6FKPxxgf</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>vVQcGxl1</t>
         </is>
-      </c>
-      <c r="O2" t="n">
-        <v>-3</v>
       </c>
       <c r="P2" t="n">
         <v>-3</v>
       </c>
       <c r="Q2" t="n">
+        <v>-3</v>
+      </c>
+      <c r="R2" t="n">
         <v>-4</v>
       </c>
-      <c r="R2" t="n">
+      <c r="S2" t="n">
         <v>-2</v>
       </c>
-      <c r="S2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr"/>
-      <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="inlineStr"/>
-      <c r="AA2" t="inlineStr"/>
-      <c r="AB2" t="inlineStr"/>
-      <c r="AC2" t="inlineStr"/>
-      <c r="AD2" t="inlineStr"/>
-      <c r="AE2" t="inlineStr"/>
-      <c r="AF2" t="inlineStr"/>
+      <c r="T2" t="n">
+        <v>2.719642857142816</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0.05162337662337535</v>
+      </c>
+      <c r="V2" t="n">
+        <v>-8.279220779220779</v>
+      </c>
+      <c r="W2" t="n">
+        <v>-11534228.8961039</v>
+      </c>
+      <c r="X2" t="n">
+        <v>-0.3747165532879819</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>-7.081980519480524</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>4.636490493633374</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>-0.4025974025974028</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>-6.515774899703459</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>-5720895.473574045</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>-9.022119745334038</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>-1.740602651316937</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>0</v>
+      </c>
       <c r="AG2" t="inlineStr"/>
       <c r="AH2" t="inlineStr"/>
       <c r="AI2" t="inlineStr"/>
@@ -823,56 +839,28 @@
       <c r="AL2" t="inlineStr"/>
       <c r="AM2" t="inlineStr"/>
       <c r="AN2" t="inlineStr"/>
-      <c r="AO2" t="n">
-        <v>-7.778598484848487</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>-11839000.9469697</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>-7.716477272727289</v>
-      </c>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
       <c r="AR2" t="inlineStr"/>
       <c r="AS2" t="inlineStr"/>
-      <c r="AT2" t="n">
-        <v>4.259765466015466</v>
-      </c>
+      <c r="AT2" t="inlineStr"/>
       <c r="AU2" t="inlineStr"/>
-      <c r="AV2" t="n">
-        <v>-0.4121212121212126</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>1.241098484848482</v>
-      </c>
+      <c r="AV2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr"/>
       <c r="AX2" t="inlineStr"/>
-      <c r="AY2" t="n">
-        <v>-2.31424501424501</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>2.890340909090895</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>-0.3693121693121693</v>
-      </c>
+      <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr"/>
+      <c r="BA2" t="inlineStr"/>
       <c r="BB2" t="inlineStr"/>
       <c r="BC2" t="inlineStr"/>
-      <c r="BD2" t="n">
-        <v>-9.221041921041916</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>-6.116012922262925</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>-5470845.861314612</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>0</v>
-      </c>
+      <c r="BD2" t="inlineStr"/>
+      <c r="BE2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>ripawyyS</t>
+          <t>M5VGwpVA</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
@@ -880,86 +868,112 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">delajod w 
+          <t xml:space="preserve">wattellier e 
   fra </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade de l abbe deschamps
-  auxerre </t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>MTLr36WA</t>
-        </is>
+          <t xml:space="preserve">stade de la mosson
+  montpellier </t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>20484</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>YagoQJpq</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
+          <t>Eyf00syR</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>nP6UzIU1</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
         <v>55</v>
       </c>
-      <c r="H3" t="n">
+      <c r="I3" t="n">
         <v>551</v>
       </c>
-      <c r="I3" t="n">
-        <v>0</v>
-      </c>
       <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
         <v>20242025</v>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>france</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>ligue 1</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>OpNm82MB</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>zuUcoUwO</t>
-        </is>
-      </c>
-      <c r="O3" t="n">
+          <t>d0X3cO3I</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>AaLVdEGK</t>
+        </is>
+      </c>
+      <c r="P3" t="n">
+        <v>-4</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="n">
         <v>5</v>
       </c>
-      <c r="P3" t="n">
-        <v>-1</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>8</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
       <c r="S3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr"/>
-      <c r="W3" t="inlineStr"/>
-      <c r="X3" t="inlineStr"/>
-      <c r="Y3" t="inlineStr"/>
-      <c r="Z3" t="inlineStr"/>
-      <c r="AA3" t="inlineStr"/>
-      <c r="AB3" t="inlineStr"/>
-      <c r="AC3" t="inlineStr"/>
-      <c r="AD3" t="inlineStr"/>
-      <c r="AE3" t="inlineStr"/>
-      <c r="AF3" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="T3" t="n">
+        <v>-0.9500721500720886</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2.505772005772009</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.542279942279947</v>
+      </c>
+      <c r="W3" t="n">
+        <v>839134.1991341989</v>
+      </c>
+      <c r="X3" t="n">
+        <v>-0.08543577966303584</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>-1.494660894660896</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>-1.105491115063614</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0.1305916305916306</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>-1.128653512687123</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>138185.9678096436</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0.6642355939031006</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0.9826989881794361</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0</v>
+      </c>
       <c r="AG3" t="inlineStr"/>
       <c r="AH3" t="inlineStr"/>
       <c r="AI3" t="inlineStr"/>
@@ -968,56 +982,28 @@
       <c r="AL3" t="inlineStr"/>
       <c r="AM3" t="inlineStr"/>
       <c r="AN3" t="inlineStr"/>
-      <c r="AO3" t="n">
-        <v>-6.746323529411754</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>-10832728.94385027</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>-8.557820855614963</v>
-      </c>
+      <c r="AO3" t="inlineStr"/>
+      <c r="AP3" t="inlineStr"/>
+      <c r="AQ3" t="inlineStr"/>
       <c r="AR3" t="inlineStr"/>
       <c r="AS3" t="inlineStr"/>
-      <c r="AT3" t="n">
-        <v>0.8602071410701342</v>
-      </c>
+      <c r="AT3" t="inlineStr"/>
       <c r="AU3" t="inlineStr"/>
-      <c r="AV3" t="n">
-        <v>-0.3262032085561497</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>2.239639037433154</v>
-      </c>
+      <c r="AV3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr"/>
       <c r="AX3" t="inlineStr"/>
-      <c r="AY3" t="n">
-        <v>-0.5353574444131688</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>-2.039438502673789</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>-0.2483844414958967</v>
-      </c>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr"/>
+      <c r="BA3" t="inlineStr"/>
       <c r="BB3" t="inlineStr"/>
       <c r="BC3" t="inlineStr"/>
-      <c r="BD3" t="n">
-        <v>-8.118783617912882</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>-6.285055329946971</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>-5224656.617032778</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>0</v>
-      </c>
+      <c r="BD3" t="inlineStr"/>
+      <c r="BE3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>SOLVXEbk</t>
+          <t>zkPwWhT1</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -1031,80 +1017,106 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade oceane
-  le havre </t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>CIEe04GT</t>
-        </is>
+          <t xml:space="preserve">roazhon park
+  rennes </t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>29778</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>CjhkPw0k</t>
-        </is>
-      </c>
-      <c r="G4" t="n">
+          <t>d2nnj1IE</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>2akflumR</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
         <v>55</v>
       </c>
-      <c r="H4" t="n">
+      <c r="I4" t="n">
         <v>551</v>
       </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
       <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
         <v>20242025</v>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>france</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>ligue 1</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>25Wk0Fko</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr">
         <is>
+          <t>SIFtcwDc</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
           <t>8MdrBIUb</t>
         </is>
       </c>
-      <c r="O4" t="n">
-        <v>-9</v>
-      </c>
       <c r="P4" t="n">
-        <v>-1</v>
+        <v>-8</v>
       </c>
       <c r="Q4" t="n">
-        <v>-3</v>
+        <v>2</v>
       </c>
       <c r="R4" t="n">
-        <v>-1</v>
+        <v>-5</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr"/>
-      <c r="W4" t="inlineStr"/>
-      <c r="X4" t="inlineStr"/>
-      <c r="Y4" t="inlineStr"/>
-      <c r="Z4" t="inlineStr"/>
-      <c r="AA4" t="inlineStr"/>
-      <c r="AB4" t="inlineStr"/>
-      <c r="AC4" t="inlineStr"/>
-      <c r="AD4" t="inlineStr"/>
-      <c r="AE4" t="inlineStr"/>
-      <c r="AF4" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>-0.7889971139970839</v>
+      </c>
+      <c r="U4" t="n">
+        <v>-3.045093795093798</v>
+      </c>
+      <c r="V4" t="n">
+        <v>-0.8676587301587375</v>
+      </c>
+      <c r="W4" t="n">
+        <v>644700.5772005767</v>
+      </c>
+      <c r="X4" t="n">
+        <v>-0.1347893663047353</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.359686147186153</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2.603949179352782</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>-0.4248196248196254</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.000295768227545</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>2562093.373633344</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>-0.2671600418476743</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>-2.092775184236373</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0</v>
+      </c>
       <c r="AG4" t="inlineStr"/>
       <c r="AH4" t="inlineStr"/>
       <c r="AI4" t="inlineStr"/>
@@ -1113,56 +1125,28 @@
       <c r="AL4" t="inlineStr"/>
       <c r="AM4" t="inlineStr"/>
       <c r="AN4" t="inlineStr"/>
-      <c r="AO4" t="n">
-        <v>-10.07929292929293</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>-42145729.16666666</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>-10.52386363636361</v>
-      </c>
+      <c r="AO4" t="inlineStr"/>
+      <c r="AP4" t="inlineStr"/>
+      <c r="AQ4" t="inlineStr"/>
       <c r="AR4" t="inlineStr"/>
       <c r="AS4" t="inlineStr"/>
-      <c r="AT4" t="n">
-        <v>-2.114194868609758</v>
-      </c>
+      <c r="AT4" t="inlineStr"/>
       <c r="AU4" t="inlineStr"/>
-      <c r="AV4" t="n">
-        <v>-1.363036616161616</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>1.113226010101009</v>
-      </c>
+      <c r="AV4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr"/>
       <c r="AX4" t="inlineStr"/>
-      <c r="AY4" t="n">
-        <v>0.6490451249785458</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>2.375157828282823</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>-1.206572838687132</v>
-      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr"/>
+      <c r="BA4" t="inlineStr"/>
       <c r="BB4" t="inlineStr"/>
       <c r="BC4" t="inlineStr"/>
-      <c r="BD4" t="n">
-        <v>-10.42513491550108</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>-10.95948354519788</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>-32537750.59894048</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>0</v>
-      </c>
+      <c r="BD4" t="inlineStr"/>
+      <c r="BE4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>0js8u60b</t>
+          <t>6ehlLyFq</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
@@ -1170,86 +1154,112 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">stinat j 
+          <t xml:space="preserve">lissorgue r 
   fra </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade francis le ble
-  brest </t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Cr4VGaUl</t>
-        </is>
+          <t xml:space="preserve">stadium municipal
+  toulouse </t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>33150</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>SblU3Hee</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
+          <t>MLmY2yB1</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>veuetnGG</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
         <v>55</v>
       </c>
-      <c r="H5" t="n">
+      <c r="I5" t="n">
         <v>551</v>
       </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
       <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
         <v>20242025</v>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>france</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>ligue 1</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>UapruDaf</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>EgvyJSJo</t>
-        </is>
-      </c>
-      <c r="O5" t="n">
-        <v>-5</v>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>YTLwacK1</t>
+        </is>
       </c>
       <c r="P5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
         <v>1</v>
       </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
       <c r="S5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr"/>
-      <c r="W5" t="inlineStr"/>
-      <c r="X5" t="inlineStr"/>
-      <c r="Y5" t="inlineStr"/>
-      <c r="Z5" t="inlineStr"/>
-      <c r="AA5" t="inlineStr"/>
-      <c r="AB5" t="inlineStr"/>
-      <c r="AC5" t="inlineStr"/>
-      <c r="AD5" t="inlineStr"/>
-      <c r="AE5" t="inlineStr"/>
-      <c r="AF5" t="inlineStr"/>
+        <v>-1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0.7142857142857224</v>
+      </c>
+      <c r="U5" t="n">
+        <v>-3.415584415584419</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1274675.324675323</v>
+      </c>
+      <c r="X5" t="n">
+        <v>-0.1479177309922652</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>3.519480519480524</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0.7974801251198471</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>-0.441558441558441</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>3.55510629811873</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>1147735.641687505</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0.7277365491651153</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>-2.582229795739121</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0</v>
+      </c>
       <c r="AG5" t="inlineStr"/>
       <c r="AH5" t="inlineStr"/>
       <c r="AI5" t="inlineStr"/>
@@ -1258,56 +1268,28 @@
       <c r="AL5" t="inlineStr"/>
       <c r="AM5" t="inlineStr"/>
       <c r="AN5" t="inlineStr"/>
-      <c r="AO5" t="n">
-        <v>-2.188181818181818</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>-5179386.363636363</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>-2.147954545454553</v>
-      </c>
+      <c r="AO5" t="inlineStr"/>
+      <c r="AP5" t="inlineStr"/>
+      <c r="AQ5" t="inlineStr"/>
       <c r="AR5" t="inlineStr"/>
       <c r="AS5" t="inlineStr"/>
-      <c r="AT5" t="n">
-        <v>-4.290719358649881</v>
-      </c>
+      <c r="AT5" t="inlineStr"/>
       <c r="AU5" t="inlineStr"/>
-      <c r="AV5" t="n">
-        <v>-0.3679545454545452</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>-0.1986363636363642</v>
-      </c>
+      <c r="AV5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr"/>
       <c r="AX5" t="inlineStr"/>
-      <c r="AY5" t="n">
-        <v>-0.8670699932019588</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>-1.865151515151496</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>-0.0519513653414585</v>
-      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr"/>
+      <c r="BA5" t="inlineStr"/>
       <c r="BB5" t="inlineStr"/>
       <c r="BC5" t="inlineStr"/>
-      <c r="BD5" t="n">
-        <v>-5.058418851458725</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>-3.792648210600021</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>-4818331.279971784</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>0</v>
-      </c>
+      <c r="BD5" t="inlineStr"/>
+      <c r="BE5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>fHYrsJy3</t>
+          <t>jqSiuc6F</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -1315,86 +1297,112 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">brisard j 
+          <t xml:space="preserve">delajod w 
   fra </t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade louis ii
-  monaco </t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>2PIvr8o4</t>
-        </is>
+          <t xml:space="preserve">stade auguste delaune
+  reims </t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>21029</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>YL2QybFe</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
+          <t>tItR6sEf</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>pfDZL71o</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
         <v>55</v>
       </c>
-      <c r="H6" t="n">
+      <c r="I6" t="n">
         <v>551</v>
       </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
       <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
         <v>20242025</v>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>france</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>ligue 1</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>CWxpUrtf</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>tAufB9Mi</t>
-        </is>
-      </c>
-      <c r="O6" t="n">
-        <v>3</v>
+          <t>SIFtcwDc</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>zuUcoUwO</t>
+        </is>
       </c>
       <c r="P6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="R6" t="n">
+        <v>4</v>
+      </c>
+      <c r="S6" t="n">
         <v>1</v>
       </c>
-      <c r="S6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T6" t="inlineStr"/>
-      <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr"/>
-      <c r="W6" t="inlineStr"/>
-      <c r="X6" t="inlineStr"/>
-      <c r="Y6" t="inlineStr"/>
-      <c r="Z6" t="inlineStr"/>
-      <c r="AA6" t="inlineStr"/>
-      <c r="AB6" t="inlineStr"/>
-      <c r="AC6" t="inlineStr"/>
-      <c r="AD6" t="inlineStr"/>
-      <c r="AE6" t="inlineStr"/>
-      <c r="AF6" t="inlineStr"/>
+      <c r="T6" t="n">
+        <v>2.402020202020196</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.211875901875903</v>
+      </c>
+      <c r="V6" t="n">
+        <v>-2.221493506493502</v>
+      </c>
+      <c r="W6" t="n">
+        <v>-5439402.777777778</v>
+      </c>
+      <c r="X6" t="n">
+        <v>-0.1275615779375177</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>-2.415418470418459</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2.97326925372036</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>-0.2188383838383838</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>-0.5056606718260781</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>-3235598.634865553</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>-4.285941961129936</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>-2.928895498820307</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0</v>
+      </c>
       <c r="AG6" t="inlineStr"/>
       <c r="AH6" t="inlineStr"/>
       <c r="AI6" t="inlineStr"/>
@@ -1403,56 +1411,28 @@
       <c r="AL6" t="inlineStr"/>
       <c r="AM6" t="inlineStr"/>
       <c r="AN6" t="inlineStr"/>
-      <c r="AO6" t="n">
-        <v>6.487523258904844</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>12913308.74534822</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>7.546617490696434</v>
-      </c>
+      <c r="AO6" t="inlineStr"/>
+      <c r="AP6" t="inlineStr"/>
+      <c r="AQ6" t="inlineStr"/>
       <c r="AR6" t="inlineStr"/>
       <c r="AS6" t="inlineStr"/>
-      <c r="AT6" t="n">
-        <v>0.7703458355492785</v>
-      </c>
+      <c r="AT6" t="inlineStr"/>
       <c r="AU6" t="inlineStr"/>
-      <c r="AV6" t="n">
-        <v>0.6061868686868686</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>-1.127389021796919</v>
-      </c>
+      <c r="AV6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr"/>
       <c r="AX6" t="inlineStr"/>
-      <c r="AY6" t="n">
-        <v>-2.817144015930502</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>1.239616560340238</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>0.1995893094079739</v>
-      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr"/>
+      <c r="BA6" t="inlineStr"/>
       <c r="BB6" t="inlineStr"/>
       <c r="BC6" t="inlineStr"/>
-      <c r="BD6" t="n">
-        <v>4.978215283475677</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>7.739090076896915</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>7596270.643946451</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>0</v>
-      </c>
+      <c r="BD6" t="inlineStr"/>
+      <c r="BE6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>M5VGwpVA</t>
+          <t>ripawyyS</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
@@ -1460,86 +1440,112 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">wattellier e 
+          <t xml:space="preserve">delajod w 
   fra </t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade de la mosson
-  montpellier </t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Eyf00syR</t>
-        </is>
+          <t xml:space="preserve">stade de l abbe deschamps
+  auxerre </t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>17924</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>nP6UzIU1</t>
-        </is>
-      </c>
-      <c r="G7" t="n">
+          <t>MTLr36WA</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>YagoQJpq</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
         <v>55</v>
       </c>
-      <c r="H7" t="n">
+      <c r="I7" t="n">
         <v>551</v>
       </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
       <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
         <v>20242025</v>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>france</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>ligue 1</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>d0X3cO3I</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>AaLVdEGK</t>
-        </is>
-      </c>
-      <c r="O7" t="n">
-        <v>-4</v>
+          <t>OpNm82MB</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>zuUcoUwO</t>
+        </is>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q7" t="n">
-        <v>5</v>
+        <v>-1</v>
       </c>
       <c r="R7" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
-      <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr"/>
-      <c r="V7" t="inlineStr"/>
-      <c r="W7" t="inlineStr"/>
-      <c r="X7" t="inlineStr"/>
-      <c r="Y7" t="inlineStr"/>
-      <c r="Z7" t="inlineStr"/>
-      <c r="AA7" t="inlineStr"/>
-      <c r="AB7" t="inlineStr"/>
-      <c r="AC7" t="inlineStr"/>
-      <c r="AD7" t="inlineStr"/>
-      <c r="AE7" t="inlineStr"/>
-      <c r="AF7" t="inlineStr"/>
+      <c r="T7" t="n">
+        <v>-2.500000000000028</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2.336038961038962</v>
+      </c>
+      <c r="V7" t="n">
+        <v>-6.561688311688314</v>
+      </c>
+      <c r="W7" t="n">
+        <v>-11066030.84415585</v>
+      </c>
+      <c r="X7" t="n">
+        <v>-0.3257250268528467</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>-8.461038961038952</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>-0.686596767893775</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>-0.3246753246753251</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>-6.911510377675796</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>-6279749.970163506</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>-8.396693166899937</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>-0.4180160900085674</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0</v>
+      </c>
       <c r="AG7" t="inlineStr"/>
       <c r="AH7" t="inlineStr"/>
       <c r="AI7" t="inlineStr"/>
@@ -1548,56 +1554,28 @@
       <c r="AL7" t="inlineStr"/>
       <c r="AM7" t="inlineStr"/>
       <c r="AN7" t="inlineStr"/>
-      <c r="AO7" t="n">
-        <v>1.563383838383828</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>774507.5757575752</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>-1.714141414141409</v>
-      </c>
+      <c r="AO7" t="inlineStr"/>
+      <c r="AP7" t="inlineStr"/>
+      <c r="AQ7" t="inlineStr"/>
       <c r="AR7" t="inlineStr"/>
       <c r="AS7" t="inlineStr"/>
-      <c r="AT7" t="n">
-        <v>-1.118346064038775</v>
-      </c>
+      <c r="AT7" t="inlineStr"/>
       <c r="AU7" t="inlineStr"/>
-      <c r="AV7" t="n">
-        <v>0.1571338383838383</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>3.099116161616163</v>
-      </c>
+      <c r="AV7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr"/>
       <c r="AX7" t="inlineStr"/>
-      <c r="AY7" t="n">
-        <v>0.2867391716998995</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>-2.1883838383838</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>-0.1049475371252182</v>
-      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr"/>
+      <c r="BA7" t="inlineStr"/>
       <c r="BB7" t="inlineStr"/>
       <c r="BC7" t="inlineStr"/>
-      <c r="BD7" t="n">
-        <v>1.015734422949777</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>-0.5268338425113512</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>297530.6903279708</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>0</v>
-      </c>
+      <c r="BD7" t="inlineStr"/>
+      <c r="BE7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>jqSiuc6F</t>
+          <t>fHYrsJy3</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -1605,86 +1583,112 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">delajod w 
+          <t xml:space="preserve">brisard j 
   fra </t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade auguste delaune
-  reims </t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>tItR6sEf</t>
-        </is>
+          <t xml:space="preserve">stade louis ii
+  monaco </t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>18523</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>pfDZL71o</t>
-        </is>
-      </c>
-      <c r="G8" t="n">
+          <t>2PIvr8o4</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>YL2QybFe</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
         <v>55</v>
       </c>
-      <c r="H8" t="n">
+      <c r="I8" t="n">
         <v>551</v>
       </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
       <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
         <v>20242025</v>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>france</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>ligue 1</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>SIFtcwDc</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>zuUcoUwO</t>
-        </is>
-      </c>
-      <c r="O8" t="n">
+          <t>CWxpUrtf</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>tAufB9Mi</t>
+        </is>
+      </c>
+      <c r="P8" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>2</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6</v>
+      </c>
+      <c r="S8" t="n">
         <v>1</v>
       </c>
-      <c r="P8" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>4</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0</v>
-      </c>
-      <c r="T8" t="inlineStr"/>
-      <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr"/>
-      <c r="W8" t="inlineStr"/>
-      <c r="X8" t="inlineStr"/>
-      <c r="Y8" t="inlineStr"/>
-      <c r="Z8" t="inlineStr"/>
-      <c r="AA8" t="inlineStr"/>
-      <c r="AB8" t="inlineStr"/>
-      <c r="AC8" t="inlineStr"/>
-      <c r="AD8" t="inlineStr"/>
-      <c r="AE8" t="inlineStr"/>
-      <c r="AF8" t="inlineStr"/>
+      <c r="T8" t="n">
+        <v>0.7164764528401122</v>
+      </c>
+      <c r="U8" t="n">
+        <v>-1.126065853338581</v>
+      </c>
+      <c r="V8" t="n">
+        <v>6.570431588613403</v>
+      </c>
+      <c r="W8" t="n">
+        <v>12735890.06952643</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0.3430561698363555</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>7.616030434212263</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>1.077492856925772</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0.5518037518037517</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>7.899077074143904</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>9751131.907230277</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>5.901118966954172</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>-2.497809011906256</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0</v>
+      </c>
       <c r="AG8" t="inlineStr"/>
       <c r="AH8" t="inlineStr"/>
       <c r="AI8" t="inlineStr"/>
@@ -1693,56 +1697,28 @@
       <c r="AL8" t="inlineStr"/>
       <c r="AM8" t="inlineStr"/>
       <c r="AN8" t="inlineStr"/>
-      <c r="AO8" t="n">
-        <v>-2.064908702408701</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>-5610518.162393162</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>-2.674159867909864</v>
-      </c>
+      <c r="AO8" t="inlineStr"/>
+      <c r="AP8" t="inlineStr"/>
+      <c r="AQ8" t="inlineStr"/>
       <c r="AR8" t="inlineStr"/>
       <c r="AS8" t="inlineStr"/>
-      <c r="AT8" t="n">
-        <v>2.1298524824347</v>
-      </c>
+      <c r="AT8" t="inlineStr"/>
       <c r="AU8" t="inlineStr"/>
-      <c r="AV8" t="n">
-        <v>-0.2295114607614608</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>1.666938616938619</v>
-      </c>
+      <c r="AV8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr"/>
       <c r="AX8" t="inlineStr"/>
-      <c r="AY8" t="n">
-        <v>-2.957233642332326</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>2.050121406371346</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>-0.129117331255489</v>
-      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr"/>
+      <c r="BA8" t="inlineStr"/>
       <c r="BB8" t="inlineStr"/>
       <c r="BC8" t="inlineStr"/>
-      <c r="BD8" t="n">
-        <v>-3.102359598247745</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>0.1884778385600754</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>-1820081.427694503</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>0</v>
-      </c>
+      <c r="BD8" t="inlineStr"/>
+      <c r="BE8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>6ehlLyFq</t>
+          <t>SOLVXEbk</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
@@ -1750,86 +1726,112 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">lissorgue r 
+          <t xml:space="preserve">letexier f 
   fra </t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadium municipal
-  toulouse </t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>MLmY2yB1</t>
-        </is>
+          <t xml:space="preserve">stade oceane
+  le havre </t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>25178</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>veuetnGG</t>
-        </is>
-      </c>
-      <c r="G9" t="n">
+          <t>CIEe04GT</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>CjhkPw0k</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
         <v>55</v>
       </c>
-      <c r="H9" t="n">
+      <c r="I9" t="n">
         <v>551</v>
       </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
       <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
         <v>20242025</v>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>france</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>ligue 1</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>UapruDaf</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>YTLwacK1</t>
-        </is>
-      </c>
-      <c r="O9" t="n">
+          <t>25Wk0Fko</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>8MdrBIUb</t>
+        </is>
+      </c>
+      <c r="P9" t="n">
+        <v>-9</v>
+      </c>
+      <c r="Q9" t="n">
         <v>-1</v>
       </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1</v>
-      </c>
       <c r="R9" t="n">
+        <v>-3</v>
+      </c>
+      <c r="S9" t="n">
         <v>-1</v>
       </c>
-      <c r="S9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T9" t="inlineStr"/>
-      <c r="U9" t="inlineStr"/>
-      <c r="V9" t="inlineStr"/>
-      <c r="W9" t="inlineStr"/>
-      <c r="X9" t="inlineStr"/>
-      <c r="Y9" t="inlineStr"/>
-      <c r="Z9" t="inlineStr"/>
-      <c r="AA9" t="inlineStr"/>
-      <c r="AB9" t="inlineStr"/>
-      <c r="AC9" t="inlineStr"/>
-      <c r="AD9" t="inlineStr"/>
-      <c r="AE9" t="inlineStr"/>
-      <c r="AF9" t="inlineStr"/>
+      <c r="T9" t="n">
+        <v>2.367766955266944</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0.9788900913900918</v>
+      </c>
+      <c r="V9" t="n">
+        <v>-8.770244107744119</v>
+      </c>
+      <c r="W9" t="n">
+        <v>-33454933.86243385</v>
+      </c>
+      <c r="X9" t="n">
+        <v>-1.233638093395253</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>-9.6691317941318</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>-1.987334763710976</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>-1.216666666666666</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>-10.64779148835355</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>-33999853.09632053</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>-9.125626519677283</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1.343246985579132</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0</v>
+      </c>
       <c r="AG9" t="inlineStr"/>
       <c r="AH9" t="inlineStr"/>
       <c r="AI9" t="inlineStr"/>
@@ -1838,56 +1840,28 @@
       <c r="AL9" t="inlineStr"/>
       <c r="AM9" t="inlineStr"/>
       <c r="AN9" t="inlineStr"/>
-      <c r="AO9" t="n">
-        <v>-0.5333333333333314</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>734848.4848484844</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>3.048484848484875</v>
-      </c>
+      <c r="AO9" t="inlineStr"/>
+      <c r="AP9" t="inlineStr"/>
+      <c r="AQ9" t="inlineStr"/>
       <c r="AR9" t="inlineStr"/>
       <c r="AS9" t="inlineStr"/>
-      <c r="AT9" t="n">
-        <v>0.209326703891918</v>
-      </c>
+      <c r="AT9" t="inlineStr"/>
       <c r="AU9" t="inlineStr"/>
-      <c r="AV9" t="n">
-        <v>-0.4545454545454541</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>-3.406060606060603</v>
-      </c>
+      <c r="AV9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr"/>
       <c r="AX9" t="inlineStr"/>
-      <c r="AY9" t="n">
-        <v>-2.63731570362005</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>0.6909090909091447</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>-0.1304039358387183</v>
-      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr"/>
+      <c r="BA9" t="inlineStr"/>
       <c r="BB9" t="inlineStr"/>
       <c r="BC9" t="inlineStr"/>
-      <c r="BD9" t="n">
-        <v>0.995827320827317</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>4.086959658698802</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>1274509.437020306</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>0</v>
-      </c>
+      <c r="BD9" t="inlineStr"/>
+      <c r="BE9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>zkPwWhT1</t>
+          <t>0js8u60b</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -1895,86 +1869,112 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">letexier f 
+          <t xml:space="preserve">stinat j 
   fra </t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">roazhon park
-  rennes </t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>d2nnj1IE</t>
-        </is>
+          <t xml:space="preserve">stade francis le ble
+  brest </t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>15220</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2akflumR</t>
-        </is>
-      </c>
-      <c r="G10" t="n">
+          <t>Cr4VGaUl</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>SblU3Hee</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
         <v>55</v>
       </c>
-      <c r="H10" t="n">
+      <c r="I10" t="n">
         <v>551</v>
       </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
       <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
         <v>20242025</v>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>france</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>ligue 1</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>SIFtcwDc</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>8MdrBIUb</t>
-        </is>
-      </c>
-      <c r="O10" t="n">
-        <v>-8</v>
+          <t>UapruDaf</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>EgvyJSJo</t>
+        </is>
       </c>
       <c r="P10" t="n">
-        <v>2</v>
+        <v>-5</v>
       </c>
       <c r="Q10" t="n">
-        <v>-5</v>
+        <v>1</v>
       </c>
       <c r="R10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
       </c>
-      <c r="T10" t="inlineStr"/>
-      <c r="U10" t="inlineStr"/>
-      <c r="V10" t="inlineStr"/>
-      <c r="W10" t="inlineStr"/>
-      <c r="X10" t="inlineStr"/>
-      <c r="Y10" t="inlineStr"/>
-      <c r="Z10" t="inlineStr"/>
-      <c r="AA10" t="inlineStr"/>
-      <c r="AB10" t="inlineStr"/>
-      <c r="AC10" t="inlineStr"/>
-      <c r="AD10" t="inlineStr"/>
-      <c r="AE10" t="inlineStr"/>
-      <c r="AF10" t="inlineStr"/>
+      <c r="T10" t="n">
+        <v>-1.901298701298686</v>
+      </c>
+      <c r="U10" t="n">
+        <v>-0.505194805194801</v>
+      </c>
+      <c r="V10" t="n">
+        <v>-2.236363636363649</v>
+      </c>
+      <c r="W10" t="n">
+        <v>-5366883.116883117</v>
+      </c>
+      <c r="X10" t="n">
+        <v>-0.127140680833737</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>-1.907792207792184</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>-4.080095195973115</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>-0.3558441558441554</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>-3.874626692782371</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>-5373766.769865839</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>-4.246363808681352</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>-0.5005170489248307</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>0</v>
+      </c>
       <c r="AG10" t="inlineStr"/>
       <c r="AH10" t="inlineStr"/>
       <c r="AI10" t="inlineStr"/>
@@ -1983,51 +1983,23 @@
       <c r="AL10" t="inlineStr"/>
       <c r="AM10" t="inlineStr"/>
       <c r="AN10" t="inlineStr"/>
-      <c r="AO10" t="n">
-        <v>-0.8248272195640425</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>736741.0951621458</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>0.9887293992557176</v>
-      </c>
+      <c r="AO10" t="inlineStr"/>
+      <c r="AP10" t="inlineStr"/>
+      <c r="AQ10" t="inlineStr"/>
       <c r="AR10" t="inlineStr"/>
       <c r="AS10" t="inlineStr"/>
-      <c r="AT10" t="n">
-        <v>1.835751837832817</v>
-      </c>
+      <c r="AT10" t="inlineStr"/>
       <c r="AU10" t="inlineStr"/>
-      <c r="AV10" t="n">
-        <v>-0.4108984582668798</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>-2.613024986709199</v>
-      </c>
+      <c r="AV10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr"/>
       <c r="AX10" t="inlineStr"/>
-      <c r="AY10" t="n">
-        <v>-2.236535586981653</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>-0.4876129718234949</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>-0.1143865876186227</v>
-      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr"/>
+      <c r="BA10" t="inlineStr"/>
       <c r="BB10" t="inlineStr"/>
       <c r="BC10" t="inlineStr"/>
-      <c r="BD10" t="n">
-        <v>-1.185964125243629</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>0.9072912603301972</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>1569062.032390579</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>0</v>
-      </c>
+      <c r="BD10" t="inlineStr"/>
+      <c r="BE10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
